--- a/data/file_generation/input/data_57/意甲开赛时间_2025-10-27_01_00佛罗伦萨_VS博洛尼亚_比分2-2(0-1)标盘明细.xlsx
+++ b/data/file_generation/input/data_57/意甲开赛时间_2025-10-27_01_00佛罗伦萨_VS博洛尼亚_比分2-2(0-1)标盘明细.xlsx
@@ -40174,26 +40174,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4EB06117-3830-409C-9489-5B8F57FA80A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{531EBC93-64B5-4156-869C-CD8B297032EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68F64BFA-CC13-4158-AE63-5CD870CE0789}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24AC7400-0547-4967-AB25-4D8B4B871597}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D763B4B3-8C11-4624-8DF1-56BF8F4A3540}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA563B80-3369-43B6-BC7A-D77227E78742}"/>
 </file>